--- a/Test Results/Excel/Summary_Report.xlsx
+++ b/Test Results/Excel/Summary_Report.xlsx
@@ -498,20 +498,20 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>510</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>99.22%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0</v>
@@ -535,7 +535,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
